--- a/output/pdf_financials_xlsx/VCV.xlsx
+++ b/output/pdf_financials_xlsx/VCV.xlsx
@@ -6192,55 +6192,55 @@
         <v>0.035886</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.035886</v>
+        <v>0.030783</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.052254</v>
+        <v>0.032413</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.044758</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.13095</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.126822</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.09668599999999999</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.09668599999999999</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.132792</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.06675200000000001</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.148663</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.141324</v>
       </c>
       <c r="N92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.027059</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.568225</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.380325</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.132091</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>0.132091</v>
       </c>
     </row>
     <row r="93">
@@ -10490,7 +10490,11 @@
           <t>Share-based payment reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -10594,7 +10598,11 @@
           <t>Warrant reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -11306,7 +11314,11 @@
           <t>Share-based payment reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -11406,7 +11418,11 @@
           <t>Warrant reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -12832,7 +12848,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -12932,7 +12952,11 @@
           <t>Warrant reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -13662,7 +13686,11 @@
           <t>Warrant reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -14178,7 +14206,11 @@
           <t>Warrant reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -15126,7 +15158,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -15232,7 +15268,11 @@
           <t>Warrant reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -17128,7 +17168,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -18192,7 +18236,11 @@
           <t>Share-based payment reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -18296,7 +18344,11 @@
           <t>Warrant reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -18618,7 +18670,11 @@
           <t>Share-based payment reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -18722,7 +18778,11 @@
           <t>Warrant reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -19562,7 +19622,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -19666,7 +19730,11 @@
           <t>Warrant reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -19980,7 +20048,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -20080,7 +20152,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -21222,7 +21298,11 @@
           <t>Share-based payment reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -21320,7 +21400,11 @@
           <t>Warrant reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VCV.xlsx
+++ b/output/pdf_financials_xlsx/VCV.xlsx
@@ -937,58 +937,58 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.018708</v>
+        <v>0.062706</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.039179</v>
+        <v>0.056005</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.032712</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.000134</v>
+        <v>0.602584</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.953806</v>
+        <v>0.811586</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.245128</v>
+        <v>0.481936</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.208106</v>
+        <v>0.229981</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.005071</v>
+        <v>0.094497</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.014889</v>
+        <v>0.667005</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.06127</v>
+        <v>0.698605</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>1.458778</v>
+        <v>2.517387</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.079719</v>
+        <v>0.356808</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.036753</v>
+        <v>0.321442</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.050123</v>
+        <v>0.888758</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.027031</v>
+        <v>1.256966</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.402921</v>
+        <v>0.869399</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>2.184403</v>
+        <v>0.426778</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.006286</v>
+        <v>0.219138</v>
       </c>
     </row>
     <row r="11">
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.018708</v>
+        <v>-0.062706</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-0.056005</v>
@@ -1010,46 +1010,46 @@
         <v>-0.602584</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.953806</v>
+        <v>-0.811586</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.245128</v>
+        <v>-0.481936</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.208106</v>
+        <v>-0.229981</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.005071</v>
+        <v>-0.094497</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.014889</v>
+        <v>-0.667005</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.06127</v>
+        <v>-0.698605</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-1.458778</v>
+        <v>-2.517387</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.079719</v>
+        <v>-0.356808</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.036753</v>
+        <v>-0.321442</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.050123</v>
+        <v>-0.888758</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.027031</v>
+        <v>-1.256966</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.402921</v>
+        <v>-0.869399</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-2.184403</v>
+        <v>-0.426778</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-0.006286</v>
+        <v>-0.219138</v>
       </c>
     </row>
     <row r="12">
@@ -1059,22 +1059,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.001974</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000196</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000341</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000134</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000185</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>1.6e-05</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.060732</v>
+        <v>-0.062706</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.055809</v>
+        <v>-0.056005</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.12262</v>
+        <v>-0.122961</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.60245</v>
+        <v>-0.602584</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.765392</v>
+        <v>-1.765577</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.727064</v>
+        <v>-0.7270799999999999</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.438087</v>
@@ -2236,22 +2236,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.060732</v>
+        <v>-0.062706</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.055809</v>
+        <v>-0.056005</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.12262</v>
+        <v>-0.122961</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.60245</v>
+        <v>-0.602584</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.765392</v>
+        <v>-1.765577</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.727064</v>
+        <v>-0.7270799999999999</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.438087</v>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.218929</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.162682</v>
@@ -2580,37 +2580,37 @@
         <v>0</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.028848</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.003874</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.210464</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.000143</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.005202</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.001012</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.038171</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.001819</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>4e-06</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.00664</v>
       </c>
     </row>
     <row r="35">
@@ -2681,7 +2681,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.218929</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.162682</v>
@@ -2702,37 +2702,37 @@
         <v>0</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.028848</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.003874</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.210464</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.000143</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.005202</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.001012</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.038171</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.001819</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>4e-06</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.00664</v>
       </c>
     </row>
     <row r="37">
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.218929</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.007</v>
@@ -3434,37 +3434,37 @@
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.041974</v>
+        <v>0.013126</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.035216</v>
+        <v>0.031342</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.007286</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.407921</v>
+        <v>0.197457</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.005202</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.023012</v>
+        <v>0.022</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.217881</v>
+        <v>0.17971</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.016819</v>
+        <v>0.015</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.013504</v>
+        <v>0.0135</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.02014</v>
+        <v>0.0135</v>
       </c>
     </row>
     <row r="49">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -21508,7 +21508,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
@@ -35758,14 +35758,14 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E261" s="5" t="n">
-        <v>-0.062706</v>
+        <v>0.062706</v>
       </c>
       <c r="F261" s="5" t="n">
-        <v>-0.056005</v>
+        <v>0.056005</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
@@ -35773,49 +35773,49 @@
         </is>
       </c>
       <c r="H261" s="5" t="n">
-        <v>-0.602584</v>
+        <v>0.602584</v>
       </c>
       <c r="I261" s="5" t="n">
-        <v>-0.811586</v>
+        <v>0.811586</v>
       </c>
       <c r="J261" s="5" t="n">
-        <v>-0.481936</v>
+        <v>0.481936</v>
       </c>
       <c r="K261" s="5" t="n">
-        <v>-0.229981</v>
+        <v>0.229981</v>
       </c>
       <c r="L261" s="5" t="n">
-        <v>-0.094497</v>
+        <v>0.094497</v>
       </c>
       <c r="M261" s="5" t="n">
-        <v>-0.667005</v>
+        <v>0.667005</v>
       </c>
       <c r="N261" s="5" t="n">
-        <v>-0.698605</v>
+        <v>0.698605</v>
       </c>
       <c r="O261" s="5" t="n">
-        <v>-2.517387</v>
+        <v>2.517387</v>
       </c>
       <c r="P261" s="5" t="n">
-        <v>-0.356808</v>
+        <v>0.356808</v>
       </c>
       <c r="Q261" s="5" t="n">
-        <v>-0.321442</v>
+        <v>0.321442</v>
       </c>
       <c r="R261" s="5" t="n">
-        <v>-0.888758</v>
+        <v>0.888758</v>
       </c>
       <c r="S261" s="5" t="n">
-        <v>-1.256966</v>
+        <v>1.256966</v>
       </c>
       <c r="T261" s="5" t="n">
-        <v>-0.869399</v>
+        <v>0.869399</v>
       </c>
       <c r="U261" s="5" t="n">
-        <v>-0.426778</v>
+        <v>0.426778</v>
       </c>
       <c r="V261" s="5" t="n">
-        <v>-0.219138</v>
+        <v>0.219138</v>
       </c>
     </row>
     <row r="262">
@@ -36150,7 +36150,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -44362,7 +44362,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -44996,7 +44996,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -45942,7 +45942,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -48152,7 +48152,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -49316,7 +49316,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -50382,7 +50382,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E401" s="5" t="n">

--- a/output/pdf_financials_xlsx/VCV.xlsx
+++ b/output/pdf_financials_xlsx/VCV.xlsx
@@ -778,7 +778,7 @@
         <v>0.039061</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.348114</v>
+        <v>0.378114</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.448224</v>
@@ -2181,7 +2181,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.000459</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0</v>
@@ -2242,7 +2242,7 @@
         <v>-0.056005</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.122961</v>
+        <v>-0.122502</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.602584</v>
@@ -4442,28 +4442,28 @@
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.017993</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.208576</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.293775</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.273593</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.257514</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.217071</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.073792</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.040381</v>
       </c>
       <c r="M64" s="3" t="n">
         <v>0</v>
@@ -4625,49 +4625,49 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.029415</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.026455</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.048341</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.037355</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.0295</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.039423</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.082496</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.12858</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.1309</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.161474</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.142673</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.161813</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.365314</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.412272</v>
       </c>
       <c r="S67" s="3" t="n">
-        <v>0</v>
+        <v>0.453043</v>
       </c>
     </row>
     <row r="68">
@@ -6631,7 +6631,7 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.000459</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>0</v>
@@ -7256,7 +7256,7 @@
         <v>0</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.0072</v>
       </c>
       <c r="J110" s="3" t="n">
         <v>0</v>
@@ -7302,10 +7302,10 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004586</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005252</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -7323,7 +7323,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003898</v>
       </c>
       <c r="L111" s="3" t="n">
         <v>0</v>
@@ -8741,10 +8741,10 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004586</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005252</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -8762,7 +8762,7 @@
         <v>0</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003898</v>
       </c>
       <c r="L134" s="3" t="n">
         <v>0</v>
@@ -8802,10 +8802,10 @@
         <v>-0.049247</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.112439</v>
+        <v>-0.117025</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.594662</v>
+        <v>-0.5999139999999999</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-0.513077</v>
@@ -8823,7 +8823,7 @@
         <v>-0.75026</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-0.508242</v>
+        <v>-0.51214</v>
       </c>
       <c r="L135" s="3" t="n">
         <v>-2.205178</v>
@@ -28918,7 +28918,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -30410,7 +30414,11 @@
           <t>Acquisition of Equipment</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -31040,7 +31048,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -33230,7 +33242,11 @@
           <t>Amortization expense</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -44148,7 +44164,11 @@
           <t>Directors' fees (Note 12)</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>-</t>
@@ -49632,7 +49652,11 @@
           <t>Amortization expense</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>
